--- a/layout/CATALOGOS/Tipo_Obligacion.xlsx
+++ b/layout/CATALOGOS/Tipo_Obligacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\CATALOGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8CD9509-39AD-4CF4-82C5-1F48B574E287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CA04E8-71D4-4A60-A86E-9C9CA06DF742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27405" yWindow="1410" windowWidth="19200" windowHeight="15330" xr2:uid="{E5FC2B88-6B8F-42FD-891A-F0B32CE4E50D}"/>
+    <workbookView xWindow="4788" yWindow="4380" windowWidth="17280" windowHeight="9312" xr2:uid="{E5FC2B88-6B8F-42FD-891A-F0B32CE4E50D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tipo_Obligacion" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Clave</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t xml:space="preserve">Otros tipos de obligaciones de pago </t>
+  </si>
+  <si>
+    <t>Pagos por retiros de depósitos de exigibilidad inmediata</t>
   </si>
 </sst>
 </file>
@@ -99,17 +102,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="8"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Verdana"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -127,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -135,34 +136,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,22 +488,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6E563A-3CCB-4531-B652-14ACB80EF5C8}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="3"/>
+    <col min="2" max="2" width="74.33203125" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -520,7 +513,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -528,7 +521,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -536,7 +529,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -544,7 +537,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -552,7 +545,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -560,7 +553,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -568,7 +561,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -576,7 +569,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -584,7 +577,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -592,7 +585,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -600,7 +593,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -608,11 +601,19 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
